--- a/data/guests.xlsx
+++ b/data/guests.xlsx
@@ -413,17 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,30 +440,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>总人数</t>
+          <t>预算人数</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>确认人数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>家属姓名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>桌号</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>邀请函状态</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>确认状态</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -480,27 +486,30 @@
       <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>李娜,张小宝</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>已发送</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>已确认</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>叔叔一家</t>
         </is>
@@ -518,27 +527,30 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>刘强</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>已发送</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -552,19 +564,22 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>未发送</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>大学同学</t>
         </is>
